--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -1,97 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Program" sheetId="1" r:id="rId1"/>
+    <sheet name="Program" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>Program</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>c5d4ace5fb4fff01</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>domain</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;ContentIdentity.id&gt;</t>
-  </si>
-  <si>
-    <t>enum&lt;RuleDomain&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -110,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -404,97 +407,261 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>19</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>c5d4ace5fb4fff01</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;ContentIdentity.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>enum&lt;RuleDomain&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>24007</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>24105</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>24106</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>24107</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>24204</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>24303</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>24304</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>24308</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>24405</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>24506</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>24601</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +664,16 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>24623</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,26 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>67002</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>67010</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,6 +694,156 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>980301</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>980302</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>980303</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980304</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980305</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980306</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>980307</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>980308</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>980309</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>980310</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>980311</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>980312</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>980313</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>980314</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>980315</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +844,96 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>990301</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>990302</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>990303</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>990304</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>990305</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>990306</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>990307</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>990308</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>990309</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,6 +934,76 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1000301</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1000302</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1000303</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1000304</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1000305</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1000306</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1000307</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,6 +1004,66 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1010301</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1010302</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1010303</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1010304</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1010305</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1010306</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,6 +1064,206 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1020301</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1020302</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1020303</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1020304</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1020305</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1020306</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1020307</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1020308</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1020309</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1020310</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1020311</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1020312</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1020313</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1020314</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1020315</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1020316</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1020317</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1020318</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1020319</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1020320</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,6 +1264,136 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1030301</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1030302</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1030303</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1030304</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1030305</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1030306</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1030307</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1030308</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1030309</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1030310</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1030311</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1030312</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1030313</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,6 +1394,186 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1040301</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1040302</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1040303</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1040304</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1040305</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1040306</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1040307</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1040308</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1040309</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1040310</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1040311</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1040312</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1040313</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1040314</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1040315</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1040316</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1040317</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1040318</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,6 +1574,56 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1050301</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1050302</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1050303</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1050304</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1050305</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1624,6 +1624,376 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1060301</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1060302</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1060303</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1060304</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1060305</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1060306</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1060307</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1060308</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1060309</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1060310</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1060311</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1060312</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1060313</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1060314</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1060315</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1060316</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1060317</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1060318</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1060319</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1060320</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1060321</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1060322</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1060323</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1060324</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1060325</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1060326</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1060327</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1060328</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1060329</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1060330</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1060331</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1060332</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1060333</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1060334</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1060335</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1060336</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1060337</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +1994,126 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1070301</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1070302</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1070303</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1070304</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1070305</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1070306</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1070307</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1070308</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1070309</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1070310</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1070311</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1070312</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,6 +2114,206 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1080301</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1080302</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1080303</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1080304</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1080305</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1080306</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1080307</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1080308</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1080309</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1080310</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1080311</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1080312</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1080313</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1080314</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1080315</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1080316</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1080317</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1080318</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1080319</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1080320</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J183"/>
+  <dimension ref="A1:J220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2314,6 +2314,376 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1091001</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1091002</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1091003</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1091004</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1091005</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1091006</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1091007</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1091008</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1091009</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1091010</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1091011</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1091012</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1091013</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1091014</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1091015</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1091016</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1091017</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1091018</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1091019</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1091020</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1091021</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1091022</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1091023</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1091024</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1091025</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1091026</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1091027</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1091028</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1091029</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1091030</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1091031</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1091032</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1091033</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1091034</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1091035</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1091036</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1091037</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J220"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2684,6 +2684,406 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1101001</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1101002</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1101003</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1101004</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1101005</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1101006</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1101007</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1101008</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1101009</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1101010</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1101011</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1101012</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1101013</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1101014</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1101015</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1101016</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1101017</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1101018</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1101019</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1101020</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1101021</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1101022</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1101023</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1101024</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1101025</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1101026</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1101027</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1101028</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1101029</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1101030</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1101031</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1101032</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1101033</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1101034</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1101035</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>1101036</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1101037</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1101038</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1101039</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1101040</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J260"/>
+  <dimension ref="A1:J291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3084,6 +3084,316 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1111001</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1111002</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1111003</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1111004</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1111005</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1111006</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1111007</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1111008</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1111009</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1111010</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1111011</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1111012</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1111013</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1111014</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1111015</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1111016</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1111017</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1111018</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1111019</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1111020</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1111021</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1111022</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1111023</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1111024</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1111025</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1111026</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1111027</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1111028</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1111029</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1111030</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1111031</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J291"/>
+  <dimension ref="A1:J329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3394,6 +3394,386 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1121001</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1121002</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1121003</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1121004</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1121005</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1121006</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1121007</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1121008</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1121009</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1121010</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1121011</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1121012</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1121013</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1121014</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1121015</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1121016</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1121017</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1121018</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1121019</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1121020</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1121021</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1121022</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1121023</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1121024</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1121025</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1121026</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1121027</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1121028</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1121029</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1121030</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1121031</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1121032</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1121033</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1121034</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1121035</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1121036</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1121037</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1121038</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J329"/>
+  <dimension ref="A1:J389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3774,6 +3774,606 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1131001</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1131002</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1131003</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1131004</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1131005</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1131006</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1131007</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1131008</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1131009</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1131010</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1131011</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1131012</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1131013</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1131014</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1131015</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1131016</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1131017</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1131018</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1131019</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1131020</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1131021</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1131022</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1131023</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1131024</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1131025</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1131026</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1131027</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1131028</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1131029</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>1131030</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>1131031</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>1131032</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>1131033</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>1131034</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>1131035</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>1131036</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>1131037</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>1131038</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>1131039</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>1131040</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>1131041</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>1131042</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>1131043</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>1131044</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>1131045</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>1131046</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>1131047</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>1131048</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>1131049</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>1131050</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>1131051</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>1131052</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>1131053</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>1131054</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>1131055</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>1131056</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>1131057</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>1131058</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>1131059</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>1131060</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J389"/>
+  <dimension ref="A1:J430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4374,6 +4374,416 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>1141001</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>1141002</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>1141003</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>1141004</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>1141005</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>1141006</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>1141007</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>1141008</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="n">
+        <v>1141009</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="n">
+        <v>1141010</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="n">
+        <v>1141011</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="n">
+        <v>1141012</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>1141013</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>1141014</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>1141015</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>1141016</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>1141017</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>1141018</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>1141019</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>1141020</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>1141021</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="n">
+        <v>1141022</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="n">
+        <v>1141023</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="n">
+        <v>1141024</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>1141025</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>1141026</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>1141027</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>1141028</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>1141029</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>1141030</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="n">
+        <v>1141031</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="n">
+        <v>1141032</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="n">
+        <v>1141033</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="n">
+        <v>1141034</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>1141035</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>1141036</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>1141037</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>1141038</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>1141039</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="n">
+        <v>1141040</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="n">
+        <v>1141041</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J430"/>
+  <dimension ref="A1:J440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4784,6 +4784,106 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="B431" t="n">
+        <v>1151001</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="n">
+        <v>1151002</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>1151003</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>1151004</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>1151005</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>1151006</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>1151007</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="n">
+        <v>1151008</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="n">
+        <v>1151009</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="n">
+        <v>1151010</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,6 +694,4196 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>980301</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>980302</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>980303</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>980304</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>980305</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>980306</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>980307</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>980308</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>980309</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>980310</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>980311</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>980312</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>980313</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>980314</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>980315</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>990301</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>990302</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>990303</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>990304</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>990305</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>990306</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>990307</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>990308</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>990309</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1000301</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1000302</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1000303</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1000304</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1000305</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1000306</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1000307</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1010301</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1010302</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1010303</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1010304</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1010305</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1010306</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1020301</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1020302</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1020303</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1020304</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1020305</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1020306</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1020307</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1020308</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1020309</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1020310</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1020311</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1020312</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1020313</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1020314</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1020315</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1020316</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1020317</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1020318</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1020319</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1020320</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1030301</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1030302</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1030303</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1030304</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1030305</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1030306</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1030307</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1030308</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1030309</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="n">
+        <v>1030310</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="n">
+        <v>1030311</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="n">
+        <v>1030312</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="n">
+        <v>1030313</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="n">
+        <v>1040301</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>1040302</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>1040303</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="n">
+        <v>1040304</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="n">
+        <v>1040305</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="n">
+        <v>1040306</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="n">
+        <v>1040307</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="n">
+        <v>1040308</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="n">
+        <v>1040309</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="n">
+        <v>1040310</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="n">
+        <v>1040311</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="n">
+        <v>1040312</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="n">
+        <v>1040313</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>1040314</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>1040315</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>1040316</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>1040317</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>1040318</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>1050301</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>1050302</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>1050303</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>1050304</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>1050305</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>1060301</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>1060302</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>1060303</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>1060304</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>1060305</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>1060306</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>1060307</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>1060308</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>1060309</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>1060310</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>1060311</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>1060312</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>1060313</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>1060314</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>1060315</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>1060316</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>1060317</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>1060318</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>1060319</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>1060320</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>1060321</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>1060322</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>1060323</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>1060324</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>1060325</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>1060326</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>1060327</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>1060328</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>1060329</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>1060330</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>1060331</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>1060332</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>1060333</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>1060334</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>1060335</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>1060336</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>1060337</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>1070301</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>1070302</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>1070303</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>1070304</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>1070305</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>1070306</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>1070307</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>1070308</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>1070309</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>1070310</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>1070311</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>1070312</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>1080301</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>1080302</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>1080303</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>1080304</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>1080305</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>1080306</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>1080307</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>1080308</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>1080309</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>1080310</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>1080311</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>1080312</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>1080313</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>1080314</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>1080315</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>1080316</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>1080317</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>1080318</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>1080319</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>1080320</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>1091001</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>1091002</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>1091003</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>1091004</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>1091005</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>1091006</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>1091007</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>1091008</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>1091009</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>1091010</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>1091011</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>1091012</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>1091013</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>1091014</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>1091015</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>1091016</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>1091017</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>1091018</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>1091019</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>1091020</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>1091021</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="n">
+        <v>1091022</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="n">
+        <v>1091023</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="n">
+        <v>1091024</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="n">
+        <v>1091025</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="n">
+        <v>1091026</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="n">
+        <v>1091027</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="n">
+        <v>1091028</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="n">
+        <v>1091029</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="n">
+        <v>1091030</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="n">
+        <v>1091031</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="n">
+        <v>1091032</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" t="n">
+        <v>1091033</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" t="n">
+        <v>1091034</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" t="n">
+        <v>1091035</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" t="n">
+        <v>1091036</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" t="n">
+        <v>1091037</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" t="n">
+        <v>1101001</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" t="n">
+        <v>1101002</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="n">
+        <v>1101003</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="n">
+        <v>1101004</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="n">
+        <v>1101005</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="n">
+        <v>1101006</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="n">
+        <v>1101007</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="n">
+        <v>1101008</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="n">
+        <v>1101009</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="n">
+        <v>1101010</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="n">
+        <v>1101011</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="n">
+        <v>1101012</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="n">
+        <v>1101013</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="n">
+        <v>1101014</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" t="n">
+        <v>1101015</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="n">
+        <v>1101016</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="n">
+        <v>1101017</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" t="n">
+        <v>1101018</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="n">
+        <v>1101019</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="n">
+        <v>1101020</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="B241" t="n">
+        <v>1101021</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="n">
+        <v>1101022</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="n">
+        <v>1101023</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="n">
+        <v>1101024</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" t="n">
+        <v>1101025</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" t="n">
+        <v>1101026</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="n">
+        <v>1101027</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="n">
+        <v>1101028</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="n">
+        <v>1101029</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="n">
+        <v>1101030</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="n">
+        <v>1101031</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="n">
+        <v>1101032</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="n">
+        <v>1101033</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="n">
+        <v>1101034</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="n">
+        <v>1101035</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="n">
+        <v>1101036</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="n">
+        <v>1101037</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="n">
+        <v>1101038</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" t="n">
+        <v>1101039</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="n">
+        <v>1101040</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="n">
+        <v>1111001</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" t="n">
+        <v>1111002</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="n">
+        <v>1111003</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="n">
+        <v>1111004</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="n">
+        <v>1111005</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="n">
+        <v>1111006</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="n">
+        <v>1111007</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="n">
+        <v>1111008</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="n">
+        <v>1111009</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="n">
+        <v>1111010</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" t="n">
+        <v>1111011</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" t="n">
+        <v>1111012</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" t="n">
+        <v>1111013</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" t="n">
+        <v>1111014</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" t="n">
+        <v>1111015</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" t="n">
+        <v>1111016</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="n">
+        <v>1111017</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="n">
+        <v>1111018</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="n">
+        <v>1111019</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="n">
+        <v>1111020</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="n">
+        <v>1111021</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="n">
+        <v>1111022</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" t="n">
+        <v>1111023</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="n">
+        <v>1111024</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="n">
+        <v>1111025</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="n">
+        <v>1111026</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="n">
+        <v>1111027</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="n">
+        <v>1111028</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="n">
+        <v>1111029</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="n">
+        <v>1111030</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="n">
+        <v>1111031</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" t="n">
+        <v>1121001</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" t="n">
+        <v>1121002</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" t="n">
+        <v>1121003</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" t="n">
+        <v>1121004</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" t="n">
+        <v>1121005</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" t="n">
+        <v>1121006</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" t="n">
+        <v>1121007</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" t="n">
+        <v>1121008</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" t="n">
+        <v>1121009</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" t="n">
+        <v>1121010</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" t="n">
+        <v>1121011</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" t="n">
+        <v>1121012</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" t="n">
+        <v>1121013</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" t="n">
+        <v>1121014</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" t="n">
+        <v>1121015</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" t="n">
+        <v>1121016</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" t="n">
+        <v>1121017</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" t="n">
+        <v>1121018</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" t="n">
+        <v>1121019</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" t="n">
+        <v>1121020</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" t="n">
+        <v>1121021</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" t="n">
+        <v>1121022</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" t="n">
+        <v>1121023</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="n">
+        <v>1121024</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="n">
+        <v>1121025</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="n">
+        <v>1121026</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="n">
+        <v>1121027</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="n">
+        <v>1121028</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="n">
+        <v>1121029</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" t="n">
+        <v>1121030</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" t="n">
+        <v>1121031</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" t="n">
+        <v>1121032</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" t="n">
+        <v>1121033</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" t="n">
+        <v>1121034</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" t="n">
+        <v>1121035</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" t="n">
+        <v>1121036</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" t="n">
+        <v>1121037</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" t="n">
+        <v>1121038</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" t="n">
+        <v>1131001</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" t="n">
+        <v>1131002</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" t="n">
+        <v>1131003</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" t="n">
+        <v>1131004</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" t="n">
+        <v>1131005</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" t="n">
+        <v>1131006</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" t="n">
+        <v>1131007</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" t="n">
+        <v>1131008</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" t="n">
+        <v>1131009</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" t="n">
+        <v>1131010</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" t="n">
+        <v>1131011</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" t="n">
+        <v>1131012</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" t="n">
+        <v>1131013</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" t="n">
+        <v>1131014</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" t="n">
+        <v>1131015</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" t="n">
+        <v>1131016</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" t="n">
+        <v>1131017</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" t="n">
+        <v>1131018</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" t="n">
+        <v>1131019</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" t="n">
+        <v>1131020</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="n">
+        <v>1131021</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="n">
+        <v>1131022</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="n">
+        <v>1131023</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="n">
+        <v>1131024</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="n">
+        <v>1131025</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="n">
+        <v>1131026</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="n">
+        <v>1131027</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="n">
+        <v>1131028</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="n">
+        <v>1131029</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="n">
+        <v>1131030</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="n">
+        <v>1131031</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="n">
+        <v>1131032</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="n">
+        <v>1131033</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="n">
+        <v>1131034</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="n">
+        <v>1131035</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="n">
+        <v>1131036</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="n">
+        <v>1131037</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="n">
+        <v>1131038</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="n">
+        <v>1131039</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="n">
+        <v>1131040</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="n">
+        <v>1131041</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="n">
+        <v>1131042</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="n">
+        <v>1131043</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="n">
+        <v>1131044</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="n">
+        <v>1131045</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="n">
+        <v>1131046</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="n">
+        <v>1131047</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="n">
+        <v>1131048</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="n">
+        <v>1131049</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="n">
+        <v>1131050</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="n">
+        <v>1131051</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="n">
+        <v>1131052</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="n">
+        <v>1131053</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="n">
+        <v>1131054</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="n">
+        <v>1131055</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="n">
+        <v>1131056</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="n">
+        <v>1131057</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="n">
+        <v>1131058</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="n">
+        <v>1131059</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="n">
+        <v>1131060</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="n">
+        <v>1141001</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="n">
+        <v>1141002</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="n">
+        <v>1141003</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="n">
+        <v>1141004</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="n">
+        <v>1141005</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="n">
+        <v>1141006</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="n">
+        <v>1141007</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="n">
+        <v>1141008</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="n">
+        <v>1141009</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="n">
+        <v>1141010</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="n">
+        <v>1141011</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="n">
+        <v>1141012</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="n">
+        <v>1141013</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="n">
+        <v>1141014</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="n">
+        <v>1141015</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="n">
+        <v>1141016</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="n">
+        <v>1141017</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="n">
+        <v>1141018</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="n">
+        <v>1141019</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="n">
+        <v>1141020</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="n">
+        <v>1141021</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="n">
+        <v>1141022</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="n">
+        <v>1141023</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="n">
+        <v>1141024</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="n">
+        <v>1141025</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="n">
+        <v>1141026</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="n">
+        <v>1141027</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="n">
+        <v>1141028</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="n">
+        <v>1141029</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="n">
+        <v>1141030</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="n">
+        <v>1141031</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="n">
+        <v>1141032</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="n">
+        <v>1141033</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="n">
+        <v>1141034</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="n">
+        <v>1141035</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="n">
+        <v>1141036</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="n">
+        <v>1141037</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="n">
+        <v>1141038</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="n">
+        <v>1141039</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="n">
+        <v>1141040</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="n">
+        <v>1141041</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="n">
+        <v>1151001</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="n">
+        <v>1151002</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="n">
+        <v>1151003</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="n">
+        <v>1151004</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="n">
+        <v>1151005</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="n">
+        <v>1151006</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="n">
+        <v>1151007</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="n">
+        <v>1151008</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="n">
+        <v>1151009</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="n">
+        <v>1151010</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/Program.xlsx
+++ b/config/data/Program.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Program" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Program" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,149 +499,159 @@
   </sheetPr>
   <dimension ref="A1:J440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="23.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="16.7109375" customWidth="1" style="5" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>c5d4ace5fb4fff01</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>02a7b81fbde6b77d</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;ContentIdentity.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;RuleDomain&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>24007</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24007</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,8 +660,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>24105</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24105</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -575,8 +672,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>24106</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24106</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -585,8 +684,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>24107</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>24107</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -595,8 +696,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>24204</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -605,8 +708,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>24303</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>24303</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -615,8 +720,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>24304</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>24304</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -625,8 +732,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>24308</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>24308</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -635,8 +744,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>24405</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>24405</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -645,8 +756,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>24506</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24506</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -655,8 +768,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>24601</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>24601</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -665,8 +780,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>24623</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>24623</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -675,8 +792,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>67002</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>67002</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -685,8 +804,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>67010</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>67010</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -695,8 +816,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>980301</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>980301</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -705,8 +828,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>980302</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>980302</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -715,8 +840,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>980303</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>980303</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -725,8 +852,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>980304</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>980304</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -735,8 +864,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>980305</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>980305</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -745,8 +876,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>980306</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>980306</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -755,8 +888,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>980307</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>980307</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -765,8 +900,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>980308</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>980308</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -775,8 +912,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>980309</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>980309</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -785,8 +924,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>980310</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>980310</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -795,8 +936,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>980311</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>980311</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -805,8 +948,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>980312</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>980312</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -815,8 +960,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>980313</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>980313</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -825,8 +972,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>980314</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>980314</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -835,8 +984,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>980315</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>980315</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -845,8 +996,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>990301</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>990301</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -855,8 +1008,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>990302</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>990302</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -865,8 +1020,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>990303</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>990303</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -875,8 +1032,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>990304</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>990304</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -885,8 +1044,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>990305</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>990305</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -895,8 +1056,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>990306</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>990306</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -905,8 +1068,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>990307</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>990307</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -915,8 +1080,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>990308</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>990308</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -925,8 +1092,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>990309</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>990309</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -935,8 +1104,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>1000301</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1000301</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -945,8 +1116,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>1000302</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1000302</t>
+        </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -955,8 +1128,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>1000303</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1000303</t>
+        </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -965,8 +1140,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
-        <v>1000304</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1000304</t>
+        </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -975,8 +1152,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
-        <v>1000305</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1000305</t>
+        </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -985,8 +1164,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
-        <v>1000306</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1000306</t>
+        </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -995,8 +1176,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
-        <v>1000307</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1000307</t>
+        </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1005,8 +1188,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
-        <v>1010301</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1010301</t>
+        </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1015,8 +1200,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
-        <v>1010302</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1010302</t>
+        </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1025,8 +1212,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
-        <v>1010303</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1010303</t>
+        </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1035,8 +1224,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
-        <v>1010304</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1010304</t>
+        </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1045,8 +1236,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
-        <v>1010305</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1010305</t>
+        </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1055,8 +1248,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="n">
-        <v>1010306</v>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1010306</t>
+        </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1065,8 +1260,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="n">
-        <v>1020301</v>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1040301</t>
+        </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1075,8 +1272,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="n">
-        <v>1020302</v>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1040302</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1085,8 +1284,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="n">
-        <v>1020303</v>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1040303</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1095,8 +1296,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="n">
-        <v>1020304</v>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1040304</t>
+        </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1105,8 +1308,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="n">
-        <v>1020305</v>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1040305</t>
+        </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1115,8 +1320,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="n">
-        <v>1020306</v>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1040306</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1125,8 +1332,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="n">
-        <v>1020307</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1040307</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1135,8 +1344,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="n">
-        <v>1020308</v>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1040308</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1145,8 +1356,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="n">
-        <v>1020309</v>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1040309</t>
+        </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1155,8 +1368,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="n">
-        <v>1020310</v>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1040310</t>
+        </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1165,8 +1380,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="n">
-        <v>1020311</v>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1040311</t>
+        </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1175,8 +1392,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="n">
-        <v>1020312</v>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1040312</t>
+        </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1185,8 +1404,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="n">
-        <v>1020313</v>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1040313</t>
+        </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1195,8 +1416,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="n">
-        <v>1020314</v>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1040314</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1205,8 +1428,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="n">
-        <v>1020315</v>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1040315</t>
+        </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1215,8 +1440,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="n">
-        <v>1020316</v>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1040316</t>
+        </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1225,8 +1452,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="n">
-        <v>1020317</v>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1040317</t>
+        </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1235,8 +1464,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="n">
-        <v>1020318</v>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1040318</t>
+        </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1245,8 +1476,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="n">
-        <v>1020319</v>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1050301</t>
+        </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1255,8 +1488,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="n">
-        <v>1020320</v>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1050302</t>
+        </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1265,8 +1500,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="n">
-        <v>1030301</v>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1050303</t>
+        </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -1275,8 +1512,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="n">
-        <v>1030302</v>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1050304</t>
+        </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -1285,8 +1524,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="n">
-        <v>1030303</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1050305</t>
+        </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -1295,8 +1536,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="n">
-        <v>1030304</v>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1060301</t>
+        </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -1305,8 +1548,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="n">
-        <v>1030305</v>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1060302</t>
+        </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1315,8 +1560,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="n">
-        <v>1030306</v>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1060303</t>
+        </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -1325,8 +1572,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="n">
-        <v>1030307</v>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1060304</t>
+        </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -1335,8 +1584,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="n">
-        <v>1030308</v>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1060305</t>
+        </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -1345,8 +1596,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="n">
-        <v>1030309</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1060306</t>
+        </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -1355,8 +1608,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="n">
-        <v>1030310</v>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1060307</t>
+        </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -1365,8 +1620,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="n">
-        <v>1030311</v>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1060308</t>
+        </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -1375,8 +1632,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="n">
-        <v>1030312</v>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1060309</t>
+        </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -1385,8 +1644,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="n">
-        <v>1030313</v>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1060310</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -1395,8 +1656,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="n">
-        <v>1040301</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1060311</t>
+        </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -1405,8 +1668,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="n">
-        <v>1040302</v>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1060312</t>
+        </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -1415,8 +1680,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="n">
-        <v>1040303</v>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1060313</t>
+        </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -1425,8 +1692,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="n">
-        <v>1040304</v>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1060314</t>
+        </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -1435,8 +1704,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="n">
-        <v>1040305</v>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1060315</t>
+        </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -1445,8 +1716,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="n">
-        <v>1040306</v>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1060316</t>
+        </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -1455,8 +1728,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="n">
-        <v>1040307</v>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1060317</t>
+        </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -1465,8 +1740,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="n">
-        <v>1040308</v>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1060318</t>
+        </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -1475,8 +1752,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="n">
-        <v>1040309</v>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1060319</t>
+        </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -1485,8 +1764,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="n">
-        <v>1040310</v>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1060320</t>
+        </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -1495,8 +1776,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="n">
-        <v>1040311</v>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1060321</t>
+        </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -1505,8 +1788,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="n">
-        <v>1040312</v>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1060322</t>
+        </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -1515,8 +1800,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="n">
-        <v>1040313</v>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1060323</t>
+        </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -1525,8 +1812,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="n">
-        <v>1040314</v>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1060324</t>
+        </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -1535,8 +1824,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="n">
-        <v>1040315</v>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1060325</t>
+        </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -1545,8 +1836,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="n">
-        <v>1040316</v>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1060326</t>
+        </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -1555,8 +1848,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="n">
-        <v>1040317</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1060327</t>
+        </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -1565,8 +1860,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="n">
-        <v>1040318</v>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1060328</t>
+        </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -1575,8 +1872,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" t="n">
-        <v>1050301</v>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1060329</t>
+        </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -1585,8 +1884,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="n">
-        <v>1050302</v>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1060330</t>
+        </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -1595,8 +1896,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" t="n">
-        <v>1050303</v>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1060331</t>
+        </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -1605,8 +1908,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="n">
-        <v>1050304</v>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1060332</t>
+        </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -1615,8 +1920,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="n">
-        <v>1050305</v>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1060333</t>
+        </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -1625,8 +1932,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="n">
-        <v>1060301</v>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1060334</t>
+        </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -1635,8 +1944,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="B116" t="n">
-        <v>1060302</v>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1060335</t>
+        </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -1645,8 +1956,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="n">
-        <v>1060303</v>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1060336</t>
+        </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -1655,8 +1968,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="B118" t="n">
-        <v>1060304</v>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1060337</t>
+        </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -1665,8 +1980,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="B119" t="n">
-        <v>1060305</v>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1070301</t>
+        </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -1675,8 +1992,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="n">
-        <v>1060306</v>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1070302</t>
+        </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -1685,8 +2004,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="n">
-        <v>1060307</v>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1070303</t>
+        </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -1695,8 +2016,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" t="n">
-        <v>1060308</v>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1070304</t>
+        </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -1705,8 +2028,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="B123" t="n">
-        <v>1060309</v>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1070305</t>
+        </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -1715,8 +2040,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="n">
-        <v>1060310</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1070306</t>
+        </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -1725,8 +2052,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="n">
-        <v>1060311</v>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1070307</t>
+        </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -1735,8 +2064,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="n">
-        <v>1060312</v>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1070308</t>
+        </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -1745,8 +2076,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="B127" t="n">
-        <v>1060313</v>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1070309</t>
+        </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -1755,8 +2088,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="B128" t="n">
-        <v>1060314</v>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1070310</t>
+        </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -1765,8 +2100,10 @@
       </c>
     </row>
     <row r="129">
-      <c r="B129" t="n">
-        <v>1060315</v>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1070311</t>
+        </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -1775,8 +2112,10 @@
       </c>
     </row>
     <row r="130">
-      <c r="B130" t="n">
-        <v>1060316</v>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1070312</t>
+        </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -1785,8 +2124,10 @@
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="n">
-        <v>1060317</v>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1080301</t>
+        </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -1795,8 +2136,10 @@
       </c>
     </row>
     <row r="132">
-      <c r="B132" t="n">
-        <v>1060318</v>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1080302</t>
+        </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -1805,8 +2148,10 @@
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="n">
-        <v>1060319</v>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1080303</t>
+        </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -1815,8 +2160,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="B134" t="n">
-        <v>1060320</v>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1080304</t>
+        </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -1825,8 +2172,10 @@
       </c>
     </row>
     <row r="135">
-      <c r="B135" t="n">
-        <v>1060321</v>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1080305</t>
+        </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -1835,8 +2184,10 @@
       </c>
     </row>
     <row r="136">
-      <c r="B136" t="n">
-        <v>1060322</v>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1080306</t>
+        </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -1845,8 +2196,10 @@
       </c>
     </row>
     <row r="137">
-      <c r="B137" t="n">
-        <v>1060323</v>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1080307</t>
+        </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -1855,8 +2208,10 @@
       </c>
     </row>
     <row r="138">
-      <c r="B138" t="n">
-        <v>1060324</v>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1080308</t>
+        </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -1865,8 +2220,10 @@
       </c>
     </row>
     <row r="139">
-      <c r="B139" t="n">
-        <v>1060325</v>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1080309</t>
+        </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -1875,8 +2232,10 @@
       </c>
     </row>
     <row r="140">
-      <c r="B140" t="n">
-        <v>1060326</v>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1080310</t>
+        </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -1885,8 +2244,10 @@
       </c>
     </row>
     <row r="141">
-      <c r="B141" t="n">
-        <v>1060327</v>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1080311</t>
+        </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -1895,8 +2256,10 @@
       </c>
     </row>
     <row r="142">
-      <c r="B142" t="n">
-        <v>1060328</v>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1080312</t>
+        </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -1905,8 +2268,10 @@
       </c>
     </row>
     <row r="143">
-      <c r="B143" t="n">
-        <v>1060329</v>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1080313</t>
+        </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -1915,8 +2280,10 @@
       </c>
     </row>
     <row r="144">
-      <c r="B144" t="n">
-        <v>1060330</v>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1080314</t>
+        </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -1925,8 +2292,10 @@
       </c>
     </row>
     <row r="145">
-      <c r="B145" t="n">
-        <v>1060331</v>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1080315</t>
+        </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -1935,8 +2304,10 @@
       </c>
     </row>
     <row r="146">
-      <c r="B146" t="n">
-        <v>1060332</v>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1080316</t>
+        </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -1945,8 +2316,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="B147" t="n">
-        <v>1060333</v>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1080317</t>
+        </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -1955,8 +2328,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="B148" t="n">
-        <v>1060334</v>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1080318</t>
+        </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -1965,8 +2340,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="B149" t="n">
-        <v>1060335</v>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1080319</t>
+        </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -1975,8 +2352,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="B150" t="n">
-        <v>1060336</v>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1080320</t>
+        </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -1985,8 +2364,10 @@
       </c>
     </row>
     <row r="151">
-      <c r="B151" t="n">
-        <v>1060337</v>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1091001</t>
+        </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -1995,8 +2376,10 @@
       </c>
     </row>
     <row r="152">
-      <c r="B152" t="n">
-        <v>1070301</v>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1091002</t>
+        </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -2005,8 +2388,10 @@
       </c>
     </row>
     <row r="153">
-      <c r="B153" t="n">
-        <v>1070302</v>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1091003</t>
+        </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2015,8 +2400,10 @@
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="n">
-        <v>1070303</v>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1091004</t>
+        </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2025,8 +2412,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="B155" t="n">
-        <v>1070304</v>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1091005</t>
+        </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -2035,8 +2424,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="B156" t="n">
-        <v>1070305</v>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1091006</t>
+        </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -2045,8 +2436,10 @@
       </c>
     </row>
     <row r="157">
-      <c r="B157" t="n">
-        <v>1070306</v>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1091007</t>
+        </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -2055,8 +2448,10 @@
       </c>
     </row>
     <row r="158">
-      <c r="B158" t="n">
-        <v>1070307</v>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1091008</t>
+        </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -2065,8 +2460,10 @@
       </c>
     </row>
     <row r="159">
-      <c r="B159" t="n">
-        <v>1070308</v>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1091009</t>
+        </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -2075,8 +2472,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="B160" t="n">
-        <v>1070309</v>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1091010</t>
+        </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -2085,8 +2484,10 @@
       </c>
     </row>
     <row r="161">
-      <c r="B161" t="n">
-        <v>1070310</v>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1091011</t>
+        </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -2095,8 +2496,10 @@
       </c>
     </row>
     <row r="162">
-      <c r="B162" t="n">
-        <v>1070311</v>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1091012</t>
+        </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -2105,8 +2508,10 @@
       </c>
     </row>
     <row r="163">
-      <c r="B163" t="n">
-        <v>1070312</v>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1091013</t>
+        </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -2115,8 +2520,10 @@
       </c>
     </row>
     <row r="164">
-      <c r="B164" t="n">
-        <v>1080301</v>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1091014</t>
+        </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -2125,8 +2532,10 @@
       </c>
     </row>
     <row r="165">
-      <c r="B165" t="n">
-        <v>1080302</v>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1091015</t>
+        </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -2135,8 +2544,10 @@
       </c>
     </row>
     <row r="166">
-      <c r="B166" t="n">
-        <v>1080303</v>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1091016</t>
+        </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -2145,8 +2556,10 @@
       </c>
     </row>
     <row r="167">
-      <c r="B167" t="n">
-        <v>1080304</v>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1091017</t>
+        </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -2155,8 +2568,10 @@
       </c>
     </row>
     <row r="168">
-      <c r="B168" t="n">
-        <v>1080305</v>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1091018</t>
+        </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -2165,8 +2580,10 @@
       </c>
     </row>
     <row r="169">
-      <c r="B169" t="n">
-        <v>1080306</v>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1091019</t>
+        </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -2175,8 +2592,10 @@
       </c>
     </row>
     <row r="170">
-      <c r="B170" t="n">
-        <v>1080307</v>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1091020</t>
+        </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -2185,8 +2604,10 @@
       </c>
     </row>
     <row r="171">
-      <c r="B171" t="n">
-        <v>1080308</v>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1091021</t>
+        </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -2195,8 +2616,10 @@
       </c>
     </row>
     <row r="172">
-      <c r="B172" t="n">
-        <v>1080309</v>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1091022</t>
+        </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -2205,8 +2628,10 @@
       </c>
     </row>
     <row r="173">
-      <c r="B173" t="n">
-        <v>1080310</v>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1091023</t>
+        </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -2215,8 +2640,10 @@
       </c>
     </row>
     <row r="174">
-      <c r="B174" t="n">
-        <v>1080311</v>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1091024</t>
+        </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -2225,8 +2652,10 @@
       </c>
     </row>
     <row r="175">
-      <c r="B175" t="n">
-        <v>1080312</v>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1091025</t>
+        </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -2235,8 +2664,10 @@
       </c>
     </row>
     <row r="176">
-      <c r="B176" t="n">
-        <v>1080313</v>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1091026</t>
+        </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -2245,8 +2676,10 @@
       </c>
     </row>
     <row r="177">
-      <c r="B177" t="n">
-        <v>1080314</v>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1091027</t>
+        </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -2255,8 +2688,10 @@
       </c>
     </row>
     <row r="178">
-      <c r="B178" t="n">
-        <v>1080315</v>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1091028</t>
+        </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -2265,8 +2700,10 @@
       </c>
     </row>
     <row r="179">
-      <c r="B179" t="n">
-        <v>1080316</v>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1091029</t>
+        </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -2275,8 +2712,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="B180" t="n">
-        <v>1080317</v>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1091030</t>
+        </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -2285,8 +2724,10 @@
       </c>
     </row>
     <row r="181">
-      <c r="B181" t="n">
-        <v>1080318</v>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1091031</t>
+        </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -2295,8 +2736,10 @@
       </c>
     </row>
     <row r="182">
-      <c r="B182" t="n">
-        <v>1080319</v>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1091032</t>
+        </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -2305,8 +2748,10 @@
       </c>
     </row>
     <row r="183">
-      <c r="B183" t="n">
-        <v>1080320</v>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1091033</t>
+        </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -2315,8 +2760,10 @@
       </c>
     </row>
     <row r="184">
-      <c r="B184" t="n">
-        <v>1091001</v>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1091034</t>
+        </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -2325,8 +2772,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="B185" t="n">
-        <v>1091002</v>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1091035</t>
+        </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -2335,8 +2784,10 @@
       </c>
     </row>
     <row r="186">
-      <c r="B186" t="n">
-        <v>1091003</v>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1091036</t>
+        </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -2345,8 +2796,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="B187" t="n">
-        <v>1091004</v>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1091037</t>
+        </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -2355,8 +2808,10 @@
       </c>
     </row>
     <row r="188">
-      <c r="B188" t="n">
-        <v>1091005</v>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1101001</t>
+        </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -2365,8 +2820,10 @@
       </c>
     </row>
     <row r="189">
-      <c r="B189" t="n">
-        <v>1091006</v>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1101002</t>
+        </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -2375,8 +2832,10 @@
       </c>
     </row>
     <row r="190">
-      <c r="B190" t="n">
-        <v>1091007</v>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1101003</t>
+        </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -2385,8 +2844,10 @@
       </c>
     </row>
     <row r="191">
-      <c r="B191" t="n">
-        <v>1091008</v>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1101004</t>
+        </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -2395,8 +2856,10 @@
       </c>
     </row>
     <row r="192">
-      <c r="B192" t="n">
-        <v>1091009</v>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1101005</t>
+        </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -2405,8 +2868,10 @@
       </c>
     </row>
     <row r="193">
-      <c r="B193" t="n">
-        <v>1091010</v>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1101006</t>
+        </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -2415,8 +2880,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="B194" t="n">
-        <v>1091011</v>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1101007</t>
+        </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -2425,8 +2892,10 @@
       </c>
     </row>
     <row r="195">
-      <c r="B195" t="n">
-        <v>1091012</v>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1101008</t>
+        </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -2435,8 +2904,10 @@
       </c>
     </row>
     <row r="196">
-      <c r="B196" t="n">
-        <v>1091013</v>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1101009</t>
+        </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -2445,8 +2916,10 @@
       </c>
     </row>
     <row r="197">
-      <c r="B197" t="n">
-        <v>1091014</v>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1101010</t>
+        </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -2455,8 +2928,10 @@
       </c>
     </row>
     <row r="198">
-      <c r="B198" t="n">
-        <v>1091015</v>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1101011</t>
+        </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -2465,8 +2940,10 @@
       </c>
     </row>
     <row r="199">
-      <c r="B199" t="n">
-        <v>1091016</v>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1101012</t>
+        </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -2475,8 +2952,10 @@
       </c>
     </row>
     <row r="200">
-      <c r="B200" t="n">
-        <v>1091017</v>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1101013</t>
+        </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -2485,8 +2964,10 @@
       </c>
     </row>
     <row r="201">
-      <c r="B201" t="n">
-        <v>1091018</v>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1101014</t>
+        </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -2495,8 +2976,10 @@
       </c>
     </row>
     <row r="202">
-      <c r="B202" t="n">
-        <v>1091019</v>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1101015</t>
+        </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -2505,8 +2988,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="B203" t="n">
-        <v>1091020</v>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1101016</t>
+        </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -2515,8 +3000,10 @@
       </c>
     </row>
     <row r="204">
-      <c r="B204" t="n">
-        <v>1091021</v>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1101017</t>
+        </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -2525,8 +3012,10 @@
       </c>
     </row>
     <row r="205">
-      <c r="B205" t="n">
-        <v>1091022</v>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1101018</t>
+        </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -2535,8 +3024,10 @@
       </c>
     </row>
     <row r="206">
-      <c r="B206" t="n">
-        <v>1091023</v>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1101019</t>
+        </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -2545,8 +3036,10 @@
       </c>
     </row>
     <row r="207">
-      <c r="B207" t="n">
-        <v>1091024</v>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1101020</t>
+        </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -2555,8 +3048,10 @@
       </c>
     </row>
     <row r="208">
-      <c r="B208" t="n">
-        <v>1091025</v>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1101021</t>
+        </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -2565,8 +3060,10 @@
       </c>
     </row>
     <row r="209">
-      <c r="B209" t="n">
-        <v>1091026</v>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1101022</t>
+        </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -2575,8 +3072,10 @@
       </c>
     </row>
     <row r="210">
-      <c r="B210" t="n">
-        <v>1091027</v>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1101023</t>
+        </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -2585,8 +3084,10 @@
       </c>
     </row>
     <row r="211">
-      <c r="B211" t="n">
-        <v>1091028</v>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1101024</t>
+        </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -2595,8 +3096,10 @@
       </c>
     </row>
     <row r="212">
-      <c r="B212" t="n">
-        <v>1091029</v>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1101025</t>
+        </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -2605,8 +3108,10 @@
       </c>
     </row>
     <row r="213">
-      <c r="B213" t="n">
-        <v>1091030</v>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1101026</t>
+        </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -2615,8 +3120,10 @@
       </c>
     </row>
     <row r="214">
-      <c r="B214" t="n">
-        <v>1091031</v>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1101027</t>
+        </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -2625,8 +3132,10 @@
       </c>
     </row>
     <row r="215">
-      <c r="B215" t="n">
-        <v>1091032</v>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1101028</t>
+        </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -2635,8 +3144,10 @@
       </c>
     </row>
     <row r="216">
-      <c r="B216" t="n">
-        <v>1091033</v>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1101029</t>
+        </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -2645,8 +3156,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="B217" t="n">
-        <v>1091034</v>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1101030</t>
+        </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -2655,8 +3168,10 @@
       </c>
     </row>
     <row r="218">
-      <c r="B218" t="n">
-        <v>1091035</v>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1101031</t>
+        </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -2665,8 +3180,10 @@
       </c>
     </row>
     <row r="219">
-      <c r="B219" t="n">
-        <v>1091036</v>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1101032</t>
+        </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -2675,8 +3192,10 @@
       </c>
     </row>
     <row r="220">
-      <c r="B220" t="n">
-        <v>1091037</v>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1101033</t>
+        </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -2685,8 +3204,10 @@
       </c>
     </row>
     <row r="221">
-      <c r="B221" t="n">
-        <v>1101001</v>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1101034</t>
+        </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -2695,8 +3216,10 @@
       </c>
     </row>
     <row r="222">
-      <c r="B222" t="n">
-        <v>1101002</v>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1101035</t>
+        </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -2705,8 +3228,10 @@
       </c>
     </row>
     <row r="223">
-      <c r="B223" t="n">
-        <v>1101003</v>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1101036</t>
+        </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -2715,8 +3240,10 @@
       </c>
     </row>
     <row r="224">
-      <c r="B224" t="n">
-        <v>1101004</v>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1101037</t>
+        </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -2725,8 +3252,10 @@
       </c>
     </row>
     <row r="225">
-      <c r="B225" t="n">
-        <v>1101005</v>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1101038</t>
+        </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -2735,8 +3264,10 @@
       </c>
     </row>
     <row r="226">
-      <c r="B226" t="n">
-        <v>1101006</v>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1101039</t>
+        </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -2745,8 +3276,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="B227" t="n">
-        <v>1101007</v>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1101040</t>
+        </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -2755,8 +3288,10 @@
       </c>
     </row>
     <row r="228">
-      <c r="B228" t="n">
-        <v>1101008</v>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1111001</t>
+        </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -2765,8 +3300,10 @@
       </c>
     </row>
     <row r="229">
-      <c r="B229" t="n">
-        <v>1101009</v>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1111002</t>
+        </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -2775,8 +3312,10 @@
       </c>
     </row>
     <row r="230">
-      <c r="B230" t="n">
-        <v>1101010</v>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1111003</t>
+        </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -2785,8 +3324,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="B231" t="n">
-        <v>1101011</v>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1111004</t>
+        </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -2795,8 +3336,10 @@
       </c>
     </row>
     <row r="232">
-      <c r="B232" t="n">
-        <v>1101012</v>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1111005</t>
+        </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -2805,8 +3348,10 @@
       </c>
     </row>
     <row r="233">
-      <c r="B233" t="n">
-        <v>1101013</v>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1111006</t>
+        </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -2815,8 +3360,10 @@
       </c>
     </row>
     <row r="234">
-      <c r="B234" t="n">
-        <v>1101014</v>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1111007</t>
+        </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -2825,8 +3372,10 @@
       </c>
     </row>
     <row r="235">
-      <c r="B235" t="n">
-        <v>1101015</v>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1111008</t>
+        </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -2835,8 +3384,10 @@
       </c>
     </row>
     <row r="236">
-      <c r="B236" t="n">
-        <v>1101016</v>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1111009</t>
+        </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -2845,8 +3396,10 @@
       </c>
     </row>
     <row r="237">
-      <c r="B237" t="n">
-        <v>1101017</v>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1111010</t>
+        </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -2855,8 +3408,10 @@
       </c>
     </row>
     <row r="238">
-      <c r="B238" t="n">
-        <v>1101018</v>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1111011</t>
+        </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -2865,8 +3420,10 @@
       </c>
     </row>
     <row r="239">
-      <c r="B239" t="n">
-        <v>1101019</v>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1111012</t>
+        </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -2875,8 +3432,10 @@
       </c>
     </row>
     <row r="240">
-      <c r="B240" t="n">
-        <v>1101020</v>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1111013</t>
+        </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -2885,8 +3444,10 @@
       </c>
     </row>
     <row r="241">
-      <c r="B241" t="n">
-        <v>1101021</v>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1111014</t>
+        </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -2895,8 +3456,10 @@
       </c>
     </row>
     <row r="242">
-      <c r="B242" t="n">
-        <v>1101022</v>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1111015</t>
+        </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -2905,8 +3468,10 @@
       </c>
     </row>
     <row r="243">
-      <c r="B243" t="n">
-        <v>1101023</v>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1111016</t>
+        </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -2915,8 +3480,10 @@
       </c>
     </row>
     <row r="244">
-      <c r="B244" t="n">
-        <v>1101024</v>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1111017</t>
+        </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -2925,8 +3492,10 @@
       </c>
     </row>
     <row r="245">
-      <c r="B245" t="n">
-        <v>1101025</v>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1111018</t>
+        </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -2935,8 +3504,10 @@
       </c>
     </row>
     <row r="246">
-      <c r="B246" t="n">
-        <v>1101026</v>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1111019</t>
+        </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -2945,8 +3516,10 @@
       </c>
     </row>
     <row r="247">
-      <c r="B247" t="n">
-        <v>1101027</v>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1111020</t>
+        </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -2955,8 +3528,10 @@
       </c>
     </row>
     <row r="248">
-      <c r="B248" t="n">
-        <v>1101028</v>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1111021</t>
+        </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -2965,8 +3540,10 @@
       </c>
     </row>
     <row r="249">
-      <c r="B249" t="n">
-        <v>1101029</v>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1111022</t>
+        </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -2975,8 +3552,10 @@
       </c>
     </row>
     <row r="250">
-      <c r="B250" t="n">
-        <v>1101030</v>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1111023</t>
+        </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -2985,8 +3564,10 @@
       </c>
     </row>
     <row r="251">
-      <c r="B251" t="n">
-        <v>1101031</v>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1111024</t>
+        </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -2995,8 +3576,10 @@
       </c>
     </row>
     <row r="252">
-      <c r="B252" t="n">
-        <v>1101032</v>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1111025</t>
+        </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -3005,8 +3588,10 @@
       </c>
     </row>
     <row r="253">
-      <c r="B253" t="n">
-        <v>1101033</v>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1111026</t>
+        </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -3015,8 +3600,10 @@
       </c>
     </row>
     <row r="254">
-      <c r="B254" t="n">
-        <v>1101034</v>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1111027</t>
+        </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -3025,8 +3612,10 @@
       </c>
     </row>
     <row r="255">
-      <c r="B255" t="n">
-        <v>1101035</v>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1111028</t>
+        </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -3035,8 +3624,10 @@
       </c>
     </row>
     <row r="256">
-      <c r="B256" t="n">
-        <v>1101036</v>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1111029</t>
+        </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -3045,8 +3636,10 @@
       </c>
     </row>
     <row r="257">
-      <c r="B257" t="n">
-        <v>1101037</v>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1111030</t>
+        </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -3055,8 +3648,10 @@
       </c>
     </row>
     <row r="258">
-      <c r="B258" t="n">
-        <v>1101038</v>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1111031</t>
+        </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -3065,8 +3660,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="B259" t="n">
-        <v>1101039</v>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1121001</t>
+        </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -3075,8 +3672,10 @@
       </c>
     </row>
     <row r="260">
-      <c r="B260" t="n">
-        <v>1101040</v>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1121002</t>
+        </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -3085,8 +3684,10 @@
       </c>
     </row>
     <row r="261">
-      <c r="B261" t="n">
-        <v>1111001</v>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1121003</t>
+        </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -3095,8 +3696,10 @@
       </c>
     </row>
     <row r="262">
-      <c r="B262" t="n">
-        <v>1111002</v>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1121004</t>
+        </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -3105,8 +3708,10 @@
       </c>
     </row>
     <row r="263">
-      <c r="B263" t="n">
-        <v>1111003</v>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1121005</t>
+        </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -3115,8 +3720,10 @@
       </c>
     </row>
     <row r="264">
-      <c r="B264" t="n">
-        <v>1111004</v>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1121006</t>
+        </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -3125,8 +3732,10 @@
       </c>
     </row>
     <row r="265">
-      <c r="B265" t="n">
-        <v>1111005</v>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1121007</t>
+        </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -3135,8 +3744,10 @@
       </c>
     </row>
     <row r="266">
-      <c r="B266" t="n">
-        <v>1111006</v>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>1121008</t>
+        </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -3145,8 +3756,10 @@
       </c>
     </row>
     <row r="267">
-      <c r="B267" t="n">
-        <v>1111007</v>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1121009</t>
+        </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -3155,8 +3768,10 @@
       </c>
     </row>
     <row r="268">
-      <c r="B268" t="n">
-        <v>1111008</v>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1121010</t>
+        </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -3165,8 +3780,10 @@
       </c>
     </row>
     <row r="269">
-      <c r="B269" t="n">
-        <v>1111009</v>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1121011</t>
+        </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -3175,8 +3792,10 @@
       </c>
     </row>
     <row r="270">
-      <c r="B270" t="n">
-        <v>1111010</v>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1121012</t>
+        </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -3185,8 +3804,10 @@
       </c>
     </row>
     <row r="271">
-      <c r="B271" t="n">
-        <v>1111011</v>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1121013</t>
+        </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -3195,8 +3816,10 @@
       </c>
     </row>
     <row r="272">
-      <c r="B272" t="n">
-        <v>1111012</v>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1121014</t>
+        </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -3205,8 +3828,10 @@
       </c>
     </row>
     <row r="273">
-      <c r="B273" t="n">
-        <v>1111013</v>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1121015</t>
+        </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -3215,8 +3840,10 @@
       </c>
     </row>
     <row r="274">
-      <c r="B274" t="n">
-        <v>1111014</v>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1121016</t>
+        </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -3225,8 +3852,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="B275" t="n">
-        <v>1111015</v>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1121017</t>
+        </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -3235,8 +3864,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="B276" t="n">
-        <v>1111016</v>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1121018</t>
+        </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -3245,8 +3876,10 @@
       </c>
     </row>
     <row r="277">
-      <c r="B277" t="n">
-        <v>1111017</v>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1121019</t>
+        </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -3255,8 +3888,10 @@
       </c>
     </row>
     <row r="278">
-      <c r="B278" t="n">
-        <v>1111018</v>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1121020</t>
+        </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -3265,8 +3900,10 @@
       </c>
     </row>
     <row r="279">
-      <c r="B279" t="n">
-        <v>1111019</v>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1121021</t>
+        </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -3275,8 +3912,10 @@
       </c>
     </row>
     <row r="280">
-      <c r="B280" t="n">
-        <v>1111020</v>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1121022</t>
+        </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -3285,8 +3924,10 @@
       </c>
     </row>
     <row r="281">
-      <c r="B281" t="n">
-        <v>1111021</v>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1121023</t>
+        </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -3295,8 +3936,10 @@
       </c>
     </row>
     <row r="282">
-      <c r="B282" t="n">
-        <v>1111022</v>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>1121024</t>
+        </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -3305,8 +3948,10 @@
       </c>
     </row>
     <row r="283">
-      <c r="B283" t="n">
-        <v>1111023</v>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1121025</t>
+        </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -3315,8 +3960,10 @@
       </c>
     </row>
     <row r="284">
-      <c r="B284" t="n">
-        <v>1111024</v>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1121026</t>
+        </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -3325,8 +3972,10 @@
       </c>
     </row>
     <row r="285">
-      <c r="B285" t="n">
-        <v>1111025</v>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1121027</t>
+        </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -3335,8 +3984,10 @@
       </c>
     </row>
     <row r="286">
-      <c r="B286" t="n">
-        <v>1111026</v>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1121028</t>
+        </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -3345,8 +3996,10 @@
       </c>
     </row>
     <row r="287">
-      <c r="B287" t="n">
-        <v>1111027</v>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1121029</t>
+        </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -3355,8 +4008,10 @@
       </c>
     </row>
     <row r="288">
-      <c r="B288" t="n">
-        <v>1111028</v>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1121030</t>
+        </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -3365,8 +4020,10 @@
       </c>
     </row>
     <row r="289">
-      <c r="B289" t="n">
-        <v>1111029</v>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1121031</t>
+        </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -3375,8 +4032,10 @@
       </c>
     </row>
     <row r="290">
-      <c r="B290" t="n">
-        <v>1111030</v>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1121032</t>
+        </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -3385,8 +4044,10 @@
       </c>
     </row>
     <row r="291">
-      <c r="B291" t="n">
-        <v>1111031</v>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1121033</t>
+        </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -3395,8 +4056,10 @@
       </c>
     </row>
     <row r="292">
-      <c r="B292" t="n">
-        <v>1121001</v>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1121034</t>
+        </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -3405,8 +4068,10 @@
       </c>
     </row>
     <row r="293">
-      <c r="B293" t="n">
-        <v>1121002</v>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1121035</t>
+        </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -3415,8 +4080,10 @@
       </c>
     </row>
     <row r="294">
-      <c r="B294" t="n">
-        <v>1121003</v>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1121036</t>
+        </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -3425,8 +4092,10 @@
       </c>
     </row>
     <row r="295">
-      <c r="B295" t="n">
-        <v>1121004</v>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1121037</t>
+        </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -3435,8 +4104,10 @@
       </c>
     </row>
     <row r="296">
-      <c r="B296" t="n">
-        <v>1121005</v>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>1121038</t>
+        </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -3445,8 +4116,10 @@
       </c>
     </row>
     <row r="297">
-      <c r="B297" t="n">
-        <v>1121006</v>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1131001</t>
+        </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -3455,8 +4128,10 @@
       </c>
     </row>
     <row r="298">
-      <c r="B298" t="n">
-        <v>1121007</v>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>1131002</t>
+        </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -3465,8 +4140,10 @@
       </c>
     </row>
     <row r="299">
-      <c r="B299" t="n">
-        <v>1121008</v>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1131003</t>
+        </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -3475,8 +4152,10 @@
       </c>
     </row>
     <row r="300">
-      <c r="B300" t="n">
-        <v>1121009</v>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1131004</t>
+        </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -3485,8 +4164,10 @@
       </c>
     </row>
     <row r="301">
-      <c r="B301" t="n">
-        <v>1121010</v>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1131005</t>
+        </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -3495,8 +4176,10 @@
       </c>
     </row>
     <row r="302">
-      <c r="B302" t="n">
-        <v>1121011</v>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1131006</t>
+        </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -3505,8 +4188,10 @@
       </c>
     </row>
     <row r="303">
-      <c r="B303" t="n">
-        <v>1121012</v>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>1131007</t>
+        </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -3515,8 +4200,10 @@
       </c>
     </row>
     <row r="304">
-      <c r="B304" t="n">
-        <v>1121013</v>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1131008</t>
+        </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -3525,8 +4212,10 @@
       </c>
     </row>
     <row r="305">
-      <c r="B305" t="n">
-        <v>1121014</v>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1131009</t>
+        </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -3535,8 +4224,10 @@
       </c>
     </row>
     <row r="306">
-      <c r="B306" t="n">
-        <v>1121015</v>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1131010</t>
+        </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -3545,8 +4236,10 @@
       </c>
     </row>
     <row r="307">
-      <c r="B307" t="n">
-        <v>1121016</v>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1131011</t>
+        </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -3555,8 +4248,10 @@
       </c>
     </row>
     <row r="308">
-      <c r="B308" t="n">
-        <v>1121017</v>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>1131012</t>
+        </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -3565,8 +4260,10 @@
       </c>
     </row>
     <row r="309">
-      <c r="B309" t="n">
-        <v>1121018</v>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1131013</t>
+        </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -3575,8 +4272,10 @@
       </c>
     </row>
     <row r="310">
-      <c r="B310" t="n">
-        <v>1121019</v>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1131014</t>
+        </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -3585,8 +4284,10 @@
       </c>
     </row>
     <row r="311">
-      <c r="B311" t="n">
-        <v>1121020</v>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1131015</t>
+        </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -3595,8 +4296,10 @@
       </c>
     </row>
     <row r="312">
-      <c r="B312" t="n">
-        <v>1121021</v>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1131016</t>
+        </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -3605,8 +4308,10 @@
       </c>
     </row>
     <row r="313">
-      <c r="B313" t="n">
-        <v>1121022</v>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1131017</t>
+        </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -3615,8 +4320,10 @@
       </c>
     </row>
     <row r="314">
-      <c r="B314" t="n">
-        <v>1121023</v>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1131018</t>
+        </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -3625,8 +4332,10 @@
       </c>
     </row>
     <row r="315">
-      <c r="B315" t="n">
-        <v>1121024</v>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1131019</t>
+        </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -3635,8 +4344,10 @@
       </c>
     </row>
     <row r="316">
-      <c r="B316" t="n">
-        <v>1121025</v>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>1131020</t>
+        </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -3645,8 +4356,10 @@
       </c>
     </row>
     <row r="317">
-      <c r="B317" t="n">
-        <v>1121026</v>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1131021</t>
+        </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -3655,8 +4368,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="B318" t="n">
-        <v>1121027</v>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1131022</t>
+        </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -3665,8 +4380,10 @@
       </c>
     </row>
     <row r="319">
-      <c r="B319" t="n">
-        <v>1121028</v>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>1131023</t>
+        </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -3675,8 +4392,10 @@
       </c>
     </row>
     <row r="320">
-      <c r="B320" t="n">
-        <v>1121029</v>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1131024</t>
+        </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -3685,8 +4404,10 @@
       </c>
     </row>
     <row r="321">
-      <c r="B321" t="n">
-        <v>1121030</v>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1131025</t>
+        </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -3695,8 +4416,10 @@
       </c>
     </row>
     <row r="322">
-      <c r="B322" t="n">
-        <v>1121031</v>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1131026</t>
+        </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -3705,8 +4428,10 @@
       </c>
     </row>
     <row r="323">
-      <c r="B323" t="n">
-        <v>1121032</v>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1131027</t>
+        </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -3715,8 +4440,10 @@
       </c>
     </row>
     <row r="324">
-      <c r="B324" t="n">
-        <v>1121033</v>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1131028</t>
+        </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -3725,8 +4452,10 @@
       </c>
     </row>
     <row r="325">
-      <c r="B325" t="n">
-        <v>1121034</v>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1131029</t>
+        </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -3735,8 +4464,10 @@
       </c>
     </row>
     <row r="326">
-      <c r="B326" t="n">
-        <v>1121035</v>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1131030</t>
+        </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -3745,8 +4476,10 @@
       </c>
     </row>
     <row r="327">
-      <c r="B327" t="n">
-        <v>1121036</v>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1131031</t>
+        </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -3755,8 +4488,10 @@
       </c>
     </row>
     <row r="328">
-      <c r="B328" t="n">
-        <v>1121037</v>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1131032</t>
+        </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -3765,8 +4500,10 @@
       </c>
     </row>
     <row r="329">
-      <c r="B329" t="n">
-        <v>1121038</v>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1131033</t>
+        </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -3775,8 +4512,10 @@
       </c>
     </row>
     <row r="330">
-      <c r="B330" t="n">
-        <v>1131001</v>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1131034</t>
+        </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -3785,8 +4524,10 @@
       </c>
     </row>
     <row r="331">
-      <c r="B331" t="n">
-        <v>1131002</v>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1131035</t>
+        </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -3795,8 +4536,10 @@
       </c>
     </row>
     <row r="332">
-      <c r="B332" t="n">
-        <v>1131003</v>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1131036</t>
+        </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -3805,8 +4548,10 @@
       </c>
     </row>
     <row r="333">
-      <c r="B333" t="n">
-        <v>1131004</v>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1131037</t>
+        </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -3815,8 +4560,10 @@
       </c>
     </row>
     <row r="334">
-      <c r="B334" t="n">
-        <v>1131005</v>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1131038</t>
+        </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -3825,8 +4572,10 @@
       </c>
     </row>
     <row r="335">
-      <c r="B335" t="n">
-        <v>1131006</v>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1131039</t>
+        </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -3835,8 +4584,10 @@
       </c>
     </row>
     <row r="336">
-      <c r="B336" t="n">
-        <v>1131007</v>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1131040</t>
+        </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -3845,8 +4596,10 @@
       </c>
     </row>
     <row r="337">
-      <c r="B337" t="n">
-        <v>1131008</v>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1131041</t>
+        </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -3855,8 +4608,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="B338" t="n">
-        <v>1131009</v>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1131042</t>
+        </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -3865,8 +4620,10 @@
       </c>
     </row>
     <row r="339">
-      <c r="B339" t="n">
-        <v>1131010</v>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1131043</t>
+        </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -3875,8 +4632,10 @@
       </c>
     </row>
     <row r="340">
-      <c r="B340" t="n">
-        <v>1131011</v>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1131044</t>
+        </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -3885,8 +4644,10 @@
       </c>
     </row>
     <row r="341">
-      <c r="B341" t="n">
-        <v>1131012</v>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1131045</t>
+        </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -3895,8 +4656,10 @@
       </c>
     </row>
     <row r="342">
-      <c r="B342" t="n">
-        <v>1131013</v>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1131046</t>
+        </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -3905,8 +4668,10 @@
       </c>
     </row>
     <row r="343">
-      <c r="B343" t="n">
-        <v>1131014</v>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1131047</t>
+        </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -3915,8 +4680,10 @@
       </c>
     </row>
     <row r="344">
-      <c r="B344" t="n">
-        <v>1131015</v>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1131048</t>
+        </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -3925,8 +4692,10 @@
       </c>
     </row>
     <row r="345">
-      <c r="B345" t="n">
-        <v>1131016</v>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1131049</t>
+        </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -3935,8 +4704,10 @@
       </c>
     </row>
     <row r="346">
-      <c r="B346" t="n">
-        <v>1131017</v>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1131050</t>
+        </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -3945,8 +4716,10 @@
       </c>
     </row>
     <row r="347">
-      <c r="B347" t="n">
-        <v>1131018</v>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1131051</t>
+        </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -3955,8 +4728,10 @@
       </c>
     </row>
     <row r="348">
-      <c r="B348" t="n">
-        <v>1131019</v>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>1131052</t>
+        </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -3965,8 +4740,10 @@
       </c>
     </row>
     <row r="349">
-      <c r="B349" t="n">
-        <v>1131020</v>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1131053</t>
+        </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -3975,8 +4752,10 @@
       </c>
     </row>
     <row r="350">
-      <c r="B350" t="n">
-        <v>1131021</v>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>1131054</t>
+        </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -3985,8 +4764,10 @@
       </c>
     </row>
     <row r="351">
-      <c r="B351" t="n">
-        <v>1131022</v>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1131055</t>
+        </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -3995,8 +4776,10 @@
       </c>
     </row>
     <row r="352">
-      <c r="B352" t="n">
-        <v>1131023</v>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>1131056</t>
+        </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -4005,8 +4788,10 @@
       </c>
     </row>
     <row r="353">
-      <c r="B353" t="n">
-        <v>1131024</v>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1131057</t>
+        </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -4015,8 +4800,10 @@
       </c>
     </row>
     <row r="354">
-      <c r="B354" t="n">
-        <v>1131025</v>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1131058</t>
+        </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -4025,8 +4812,10 @@
       </c>
     </row>
     <row r="355">
-      <c r="B355" t="n">
-        <v>1131026</v>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1131059</t>
+        </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -4035,8 +4824,10 @@
       </c>
     </row>
     <row r="356">
-      <c r="B356" t="n">
-        <v>1131027</v>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1131060</t>
+        </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -4045,8 +4836,10 @@
       </c>
     </row>
     <row r="357">
-      <c r="B357" t="n">
-        <v>1131028</v>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1151001</t>
+        </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -4055,8 +4848,10 @@
       </c>
     </row>
     <row r="358">
-      <c r="B358" t="n">
-        <v>1131029</v>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1151002</t>
+        </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -4065,8 +4860,10 @@
       </c>
     </row>
     <row r="359">
-      <c r="B359" t="n">
-        <v>1131030</v>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>1151003</t>
+        </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -4075,8 +4872,10 @@
       </c>
     </row>
     <row r="360">
-      <c r="B360" t="n">
-        <v>1131031</v>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1151004</t>
+        </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -4085,8 +4884,10 @@
       </c>
     </row>
     <row r="361">
-      <c r="B361" t="n">
-        <v>1131032</v>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>1151005</t>
+        </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -4095,8 +4896,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="B362" t="n">
-        <v>1131033</v>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1151006</t>
+        </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -4105,8 +4908,10 @@
       </c>
     </row>
     <row r="363">
-      <c r="B363" t="n">
-        <v>1131034</v>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1151007</t>
+        </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -4115,8 +4920,10 @@
       </c>
     </row>
     <row r="364">
-      <c r="B364" t="n">
-        <v>1131035</v>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>1151008</t>
+        </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -4125,8 +4932,10 @@
       </c>
     </row>
     <row r="365">
-      <c r="B365" t="n">
-        <v>1131036</v>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>1151009</t>
+        </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -4135,8 +4944,10 @@
       </c>
     </row>
     <row r="366">
-      <c r="B366" t="n">
-        <v>1131037</v>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>1151010</t>
+        </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -4146,7 +4957,7 @@
     </row>
     <row r="367">
       <c r="B367" t="n">
-        <v>1131038</v>
+        <v>1020301</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -4156,7 +4967,7 @@
     </row>
     <row r="368">
       <c r="B368" t="n">
-        <v>1131039</v>
+        <v>1020302</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -4166,7 +4977,7 @@
     </row>
     <row r="369">
       <c r="B369" t="n">
-        <v>1131040</v>
+        <v>1020303</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -4176,7 +4987,7 @@
     </row>
     <row r="370">
       <c r="B370" t="n">
-        <v>1131041</v>
+        <v>1020304</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -4186,7 +4997,7 @@
     </row>
     <row r="371">
       <c r="B371" t="n">
-        <v>1131042</v>
+        <v>1020305</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -4196,7 +5007,7 @@
     </row>
     <row r="372">
       <c r="B372" t="n">
-        <v>1131043</v>
+        <v>1020306</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -4206,7 +5017,7 @@
     </row>
     <row r="373">
       <c r="B373" t="n">
-        <v>1131044</v>
+        <v>1020307</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -4216,7 +5027,7 @@
     </row>
     <row r="374">
       <c r="B374" t="n">
-        <v>1131045</v>
+        <v>1020308</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -4226,7 +5037,7 @@
     </row>
     <row r="375">
       <c r="B375" t="n">
-        <v>1131046</v>
+        <v>1020309</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -4236,7 +5047,7 @@
     </row>
     <row r="376">
       <c r="B376" t="n">
-        <v>1131047</v>
+        <v>1020310</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -4246,7 +5057,7 @@
     </row>
     <row r="377">
       <c r="B377" t="n">
-        <v>1131048</v>
+        <v>1020311</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -4256,7 +5067,7 @@
     </row>
     <row r="378">
       <c r="B378" t="n">
-        <v>1131049</v>
+        <v>1020312</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -4266,7 +5077,7 @@
     </row>
     <row r="379">
       <c r="B379" t="n">
-        <v>1131050</v>
+        <v>1020313</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -4276,7 +5087,7 @@
     </row>
     <row r="380">
       <c r="B380" t="n">
-        <v>1131051</v>
+        <v>1020314</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -4286,7 +5097,7 @@
     </row>
     <row r="381">
       <c r="B381" t="n">
-        <v>1131052</v>
+        <v>1020315</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -4296,7 +5107,7 @@
     </row>
     <row r="382">
       <c r="B382" t="n">
-        <v>1131053</v>
+        <v>1020316</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -4306,7 +5117,7 @@
     </row>
     <row r="383">
       <c r="B383" t="n">
-        <v>1131054</v>
+        <v>1020317</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -4316,7 +5127,7 @@
     </row>
     <row r="384">
       <c r="B384" t="n">
-        <v>1131055</v>
+        <v>1020318</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -4326,7 +5137,7 @@
     </row>
     <row r="385">
       <c r="B385" t="n">
-        <v>1131056</v>
+        <v>1020319</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -4336,7 +5147,7 @@
     </row>
     <row r="386">
       <c r="B386" t="n">
-        <v>1131057</v>
+        <v>1020320</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -4346,7 +5157,7 @@
     </row>
     <row r="387">
       <c r="B387" t="n">
-        <v>1131058</v>
+        <v>1141001</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -4356,7 +5167,7 @@
     </row>
     <row r="388">
       <c r="B388" t="n">
-        <v>1131059</v>
+        <v>1141002</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -4366,7 +5177,7 @@
     </row>
     <row r="389">
       <c r="B389" t="n">
-        <v>1131060</v>
+        <v>1141003</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -4376,7 +5187,7 @@
     </row>
     <row r="390">
       <c r="B390" t="n">
-        <v>1141001</v>
+        <v>1141004</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -4386,7 +5197,7 @@
     </row>
     <row r="391">
       <c r="B391" t="n">
-        <v>1141002</v>
+        <v>1141005</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -4396,7 +5207,7 @@
     </row>
     <row r="392">
       <c r="B392" t="n">
-        <v>1141003</v>
+        <v>1141006</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -4406,7 +5217,7 @@
     </row>
     <row r="393">
       <c r="B393" t="n">
-        <v>1141004</v>
+        <v>1141007</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -4416,7 +5227,7 @@
     </row>
     <row r="394">
       <c r="B394" t="n">
-        <v>1141005</v>
+        <v>1141008</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -4426,7 +5237,7 @@
     </row>
     <row r="395">
       <c r="B395" t="n">
-        <v>1141006</v>
+        <v>1141009</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -4436,7 +5247,7 @@
     </row>
     <row r="396">
       <c r="B396" t="n">
-        <v>1141007</v>
+        <v>1141010</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -4446,7 +5257,7 @@
     </row>
     <row r="397">
       <c r="B397" t="n">
-        <v>1141008</v>
+        <v>1141011</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -4456,7 +5267,7 @@
     </row>
     <row r="398">
       <c r="B398" t="n">
-        <v>1141009</v>
+        <v>1141012</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -4466,7 +5277,7 @@
     </row>
     <row r="399">
       <c r="B399" t="n">
-        <v>1141010</v>
+        <v>1141013</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -4476,7 +5287,7 @@
     </row>
     <row r="400">
       <c r="B400" t="n">
-        <v>1141011</v>
+        <v>1141014</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -4486,7 +5297,7 @@
     </row>
     <row r="401">
       <c r="B401" t="n">
-        <v>1141012</v>
+        <v>1141015</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -4496,7 +5307,7 @@
     </row>
     <row r="402">
       <c r="B402" t="n">
-        <v>1141013</v>
+        <v>1141016</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -4506,7 +5317,7 @@
     </row>
     <row r="403">
       <c r="B403" t="n">
-        <v>1141014</v>
+        <v>1141017</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -4516,7 +5327,7 @@
     </row>
     <row r="404">
       <c r="B404" t="n">
-        <v>1141015</v>
+        <v>1141018</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -4526,7 +5337,7 @@
     </row>
     <row r="405">
       <c r="B405" t="n">
-        <v>1141016</v>
+        <v>1141019</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -4536,7 +5347,7 @@
     </row>
     <row r="406">
       <c r="B406" t="n">
-        <v>1141017</v>
+        <v>1141020</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -4546,7 +5357,7 @@
     </row>
     <row r="407">
       <c r="B407" t="n">
-        <v>1141018</v>
+        <v>1141021</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -4556,7 +5367,7 @@
     </row>
     <row r="408">
       <c r="B408" t="n">
-        <v>1141019</v>
+        <v>1141022</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -4566,7 +5377,7 @@
     </row>
     <row r="409">
       <c r="B409" t="n">
-        <v>1141020</v>
+        <v>1141023</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -4576,7 +5387,7 @@
     </row>
     <row r="410">
       <c r="B410" t="n">
-        <v>1141021</v>
+        <v>1141024</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -4586,7 +5397,7 @@
     </row>
     <row r="411">
       <c r="B411" t="n">
-        <v>1141022</v>
+        <v>1141025</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
@@ -4596,7 +5407,7 @@
     </row>
     <row r="412">
       <c r="B412" t="n">
-        <v>1141023</v>
+        <v>1141026</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -4606,7 +5417,7 @@
     </row>
     <row r="413">
       <c r="B413" t="n">
-        <v>1141024</v>
+        <v>1141027</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -4616,7 +5427,7 @@
     </row>
     <row r="414">
       <c r="B414" t="n">
-        <v>1141025</v>
+        <v>1141028</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -4626,7 +5437,7 @@
     </row>
     <row r="415">
       <c r="B415" t="n">
-        <v>1141026</v>
+        <v>1141029</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -4636,7 +5447,7 @@
     </row>
     <row r="416">
       <c r="B416" t="n">
-        <v>1141027</v>
+        <v>1141030</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -4646,7 +5457,7 @@
     </row>
     <row r="417">
       <c r="B417" t="n">
-        <v>1141028</v>
+        <v>1141031</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -4656,7 +5467,7 @@
     </row>
     <row r="418">
       <c r="B418" t="n">
-        <v>1141029</v>
+        <v>1141032</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -4666,7 +5477,7 @@
     </row>
     <row r="419">
       <c r="B419" t="n">
-        <v>1141030</v>
+        <v>1141033</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
@@ -4676,7 +5487,7 @@
     </row>
     <row r="420">
       <c r="B420" t="n">
-        <v>1141031</v>
+        <v>1141034</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -4686,7 +5497,7 @@
     </row>
     <row r="421">
       <c r="B421" t="n">
-        <v>1141032</v>
+        <v>1141035</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -4696,7 +5507,7 @@
     </row>
     <row r="422">
       <c r="B422" t="n">
-        <v>1141033</v>
+        <v>1141036</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -4706,7 +5517,7 @@
     </row>
     <row r="423">
       <c r="B423" t="n">
-        <v>1141034</v>
+        <v>1141037</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -4716,7 +5527,7 @@
     </row>
     <row r="424">
       <c r="B424" t="n">
-        <v>1141035</v>
+        <v>1141038</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -4726,7 +5537,7 @@
     </row>
     <row r="425">
       <c r="B425" t="n">
-        <v>1141036</v>
+        <v>1141039</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -4736,7 +5547,7 @@
     </row>
     <row r="426">
       <c r="B426" t="n">
-        <v>1141037</v>
+        <v>1141040</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -4746,7 +5557,7 @@
     </row>
     <row r="427">
       <c r="B427" t="n">
-        <v>1141038</v>
+        <v>1141041</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -4756,7 +5567,7 @@
     </row>
     <row r="428">
       <c r="B428" t="n">
-        <v>1141039</v>
+        <v>1030301</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -4766,7 +5577,7 @@
     </row>
     <row r="429">
       <c r="B429" t="n">
-        <v>1141040</v>
+        <v>1030302</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -4776,7 +5587,7 @@
     </row>
     <row r="430">
       <c r="B430" t="n">
-        <v>1141041</v>
+        <v>1030303</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -4786,7 +5597,7 @@
     </row>
     <row r="431">
       <c r="B431" t="n">
-        <v>1151001</v>
+        <v>1030304</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -4796,7 +5607,7 @@
     </row>
     <row r="432">
       <c r="B432" t="n">
-        <v>1151002</v>
+        <v>1030305</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -4806,7 +5617,7 @@
     </row>
     <row r="433">
       <c r="B433" t="n">
-        <v>1151003</v>
+        <v>1030306</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -4816,7 +5627,7 @@
     </row>
     <row r="434">
       <c r="B434" t="n">
-        <v>1151004</v>
+        <v>1030307</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -4826,7 +5637,7 @@
     </row>
     <row r="435">
       <c r="B435" t="n">
-        <v>1151005</v>
+        <v>1030308</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
@@ -4836,7 +5647,7 @@
     </row>
     <row r="436">
       <c r="B436" t="n">
-        <v>1151006</v>
+        <v>1030309</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
@@ -4846,7 +5657,7 @@
     </row>
     <row r="437">
       <c r="B437" t="n">
-        <v>1151007</v>
+        <v>1030310</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -4856,7 +5667,7 @@
     </row>
     <row r="438">
       <c r="B438" t="n">
-        <v>1151008</v>
+        <v>1030311</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -4866,7 +5677,7 @@
     </row>
     <row r="439">
       <c r="B439" t="n">
-        <v>1151009</v>
+        <v>1030312</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -4876,7 +5687,7 @@
     </row>
     <row r="440">
       <c r="B440" t="n">
-        <v>1151010</v>
+        <v>1030313</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -4885,6 +5696,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Battle, Activity" promptTitle="RuleDomain enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Battle,Activity"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>